--- a/data/auto_synced/Financial_Model_25MT_Uttar_Pradesh.xlsx
+++ b/data/auto_synced/Financial_Model_25MT_Uttar_Pradesh.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03 April 2026</t>
+          <t>04 April 2026</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rs 6.00 Crore</t>
+          <t>Rs 5.00 Crore</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rs 4.00 Crore</t>
+          <t>Rs 5.00 Crore</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rs 10.43 Lakhs</t>
+          <t>Rs 9.37 Lakhs</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rs 1061 Lakhs</t>
+          <t>Rs 1026 Lakhs</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs 18.2 Lakhs</t>
+          <t>Rs 17.1 Lakhs</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.01x</t>
+          <t>2.14x</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>52 months</t>
+          <t>54 months</t>
         </is>
       </c>
     </row>
@@ -746,40 +746,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1240</v>
+        <v>1200</v>
       </c>
       <c r="D2" t="n">
-        <v>499.1</v>
+        <v>483</v>
       </c>
       <c r="E2" t="n">
-        <v>260.4</v>
+        <v>252</v>
       </c>
       <c r="F2" t="n">
         <v>46.5</v>
       </c>
       <c r="G2" t="n">
-        <v>192.2</v>
+        <v>184.5</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" t="n">
-        <v>23.2</v>
+        <v>14.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>3.62</v>
       </c>
       <c r="L2" t="n">
-        <v>17.4</v>
+        <v>10.88</v>
       </c>
       <c r="M2" t="n">
-        <v>117.4</v>
+        <v>110.88</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
@@ -792,40 +792,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1705</v>
+        <v>1650</v>
       </c>
       <c r="D3" t="n">
-        <v>686.26</v>
+        <v>664.13</v>
       </c>
       <c r="E3" t="n">
-        <v>358.05</v>
+        <v>346.5</v>
       </c>
       <c r="F3" t="n">
         <v>46.5</v>
       </c>
       <c r="G3" t="n">
-        <v>281.71</v>
+        <v>271.13</v>
       </c>
       <c r="H3" t="n">
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" t="n">
-        <v>112.71</v>
+        <v>101.13</v>
       </c>
       <c r="K3" t="n">
-        <v>28.18</v>
+        <v>25.28</v>
       </c>
       <c r="L3" t="n">
-        <v>84.53</v>
+        <v>75.84</v>
       </c>
       <c r="M3" t="n">
-        <v>184.53</v>
+        <v>175.84</v>
       </c>
       <c r="N3" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="4">
@@ -838,40 +838,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="D4" t="n">
-        <v>873.42</v>
+        <v>845.25</v>
       </c>
       <c r="E4" t="n">
-        <v>455.7</v>
+        <v>441</v>
       </c>
       <c r="F4" t="n">
         <v>46.5</v>
       </c>
       <c r="G4" t="n">
-        <v>371.22</v>
+        <v>357.75</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J4" t="n">
-        <v>202.22</v>
+        <v>187.75</v>
       </c>
       <c r="K4" t="n">
-        <v>50.56</v>
+        <v>46.94</v>
       </c>
       <c r="L4" t="n">
-        <v>151.67</v>
+        <v>140.81</v>
       </c>
       <c r="M4" t="n">
-        <v>251.67</v>
+        <v>240.81</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="5">
@@ -884,40 +884,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2480</v>
+        <v>2400</v>
       </c>
       <c r="D5" t="n">
-        <v>998.2</v>
+        <v>966</v>
       </c>
       <c r="E5" t="n">
-        <v>520.8</v>
+        <v>504</v>
       </c>
       <c r="F5" t="n">
         <v>46.5</v>
       </c>
       <c r="G5" t="n">
-        <v>430.9</v>
+        <v>415.5</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J5" t="n">
-        <v>261.9</v>
+        <v>245.5</v>
       </c>
       <c r="K5" t="n">
-        <v>65.48</v>
+        <v>61.38</v>
       </c>
       <c r="L5" t="n">
-        <v>196.43</v>
+        <v>184.12</v>
       </c>
       <c r="M5" t="n">
-        <v>296.43</v>
+        <v>284.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="6">
@@ -930,40 +930,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2635</v>
+        <v>2550</v>
       </c>
       <c r="D6" t="n">
-        <v>1060.59</v>
+        <v>1026.38</v>
       </c>
       <c r="E6" t="n">
-        <v>553.35</v>
+        <v>535.5</v>
       </c>
       <c r="F6" t="n">
         <v>46.5</v>
       </c>
       <c r="G6" t="n">
-        <v>460.74</v>
+        <v>444.38</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" t="n">
-        <v>291.74</v>
+        <v>274.38</v>
       </c>
       <c r="K6" t="n">
-        <v>72.93000000000001</v>
+        <v>68.59</v>
       </c>
       <c r="L6" t="n">
-        <v>218.8</v>
+        <v>205.78</v>
       </c>
       <c r="M6" t="n">
-        <v>318.8</v>
+        <v>305.78</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="7">
@@ -976,40 +976,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2790</v>
+        <v>2700</v>
       </c>
       <c r="D7" t="n">
-        <v>1122.97</v>
+        <v>1086.75</v>
       </c>
       <c r="E7" t="n">
-        <v>585.9</v>
+        <v>567</v>
       </c>
       <c r="F7" t="n">
         <v>46.5</v>
       </c>
       <c r="G7" t="n">
-        <v>490.57</v>
+        <v>473.25</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" t="n">
-        <v>321.57</v>
+        <v>303.25</v>
       </c>
       <c r="K7" t="n">
-        <v>80.39</v>
+        <v>75.81</v>
       </c>
       <c r="L7" t="n">
-        <v>241.18</v>
+        <v>227.44</v>
       </c>
       <c r="M7" t="n">
-        <v>341.18</v>
+        <v>327.44</v>
       </c>
       <c r="N7" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="8">
@@ -1022,40 +1022,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2790</v>
+        <v>2700</v>
       </c>
       <c r="D8" t="n">
-        <v>1122.97</v>
+        <v>1086.75</v>
       </c>
       <c r="E8" t="n">
-        <v>585.9</v>
+        <v>567</v>
       </c>
       <c r="F8" t="n">
         <v>46.5</v>
       </c>
       <c r="G8" t="n">
-        <v>490.57</v>
+        <v>473.25</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" t="n">
-        <v>321.57</v>
+        <v>303.25</v>
       </c>
       <c r="K8" t="n">
-        <v>80.39</v>
+        <v>75.81</v>
       </c>
       <c r="L8" t="n">
-        <v>241.18</v>
+        <v>227.44</v>
       </c>
       <c r="M8" t="n">
-        <v>341.18</v>
+        <v>327.44</v>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
     </row>
   </sheetData>
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>281.2</v>
+        <v>270.2</v>
       </c>
       <c r="C2" t="n">
-        <v>419.6</v>
+        <v>404.1</v>
       </c>
       <c r="D2" t="n">
-        <v>557.9</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>170.6</v>
+        <v>163.1</v>
       </c>
       <c r="C3" t="n">
-        <v>308.9</v>
+        <v>297</v>
       </c>
       <c r="D3" t="n">
-        <v>447.2</v>
+        <v>430.9</v>
       </c>
     </row>
     <row r="4">
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.9</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>198.2</v>
+        <v>189.9</v>
       </c>
       <c r="D4" t="n">
-        <v>336.6</v>
+        <v>323.8</v>
       </c>
     </row>
   </sheetData>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
